--- a/assets/fcf/Financial Statements & Free Cash Flow.xlsx
+++ b/assets/fcf/Financial Statements & Free Cash Flow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\Financial Analytics\Course\5 - Financial Statements &amp; Free Cash Flows\1 - Async\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\5 - Financial Statements &amp; Free Cash Flow\1 - Async\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB80040-4CD8-4A40-8BD4-F7330BC5A073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CB26C1-CB3D-4E92-92FC-7A3F89469874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16354" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" activeTab="1" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Description" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="85">
   <si>
     <t>Cash</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>Sales is projected to be $1000 with a gross profit margin of 30% (i.e. $700 in COGS) in years 1 through 3.</t>
+  </si>
+  <si>
+    <t>=EBIT</t>
   </si>
 </sst>
 </file>
@@ -432,7 +435,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -558,6 +561,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -897,79 +903,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CDAEB0D-3A27-486D-AC6C-E43C29FCDDD3}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>80</v>
       </c>
@@ -982,18 +988,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4551FB90-26B1-44C9-90FF-AB3D820DD8A7}">
   <dimension ref="A1:L57"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="30.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.08984375" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="7.6328125" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.81640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="53.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.06640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="7.59765625" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.796875" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="6.06640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="53.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="64" t="s">
         <v>16</v>
       </c>
@@ -1008,7 +1014,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="65" t="s">
         <v>17</v>
       </c>
@@ -1029,7 +1035,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="66" t="s">
         <v>30</v>
       </c>
@@ -1056,7 +1062,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="67" t="s">
         <v>18</v>
       </c>
@@ -1071,9 +1077,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="68" t="s">
-        <v>19</v>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A5" s="71" t="s">
+        <v>84</v>
       </c>
       <c r="B5" s="68"/>
       <c r="C5" s="43"/>
@@ -1081,7 +1087,7 @@
       <c r="E5" s="43"/>
       <c r="J5" s="24"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="67" t="s">
         <v>20</v>
       </c>
@@ -1093,7 +1099,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="66" t="s">
         <v>21</v>
       </c>
@@ -1102,7 +1108,7 @@
       <c r="D7" s="43"/>
       <c r="E7" s="43"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="67" t="s">
         <v>22</v>
       </c>
@@ -1114,7 +1120,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="69" t="s">
         <v>23</v>
       </c>
@@ -1123,7 +1129,7 @@
       <c r="D9" s="45"/>
       <c r="E9" s="45"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="70" t="s">
         <v>33</v>
       </c>
@@ -1134,7 +1140,7 @@
       <c r="F10" s="27"/>
       <c r="G10" s="27"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="70" t="s">
         <v>34</v>
       </c>
@@ -1146,7 +1152,7 @@
       <c r="G11" s="27"/>
       <c r="I11" s="29"/>
     </row>
-    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="62" t="s">
         <v>59</v>
       </c>
@@ -1161,7 +1167,7 @@
       <c r="J14" s="62"/>
       <c r="K14" s="62"/>
     </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1193,7 +1199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
         <v>0</v>
       </c>
@@ -1215,7 +1221,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
         <v>1</v>
       </c>
@@ -1237,7 +1243,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" s="11" t="s">
         <v>2</v>
       </c>
@@ -1256,7 +1262,7 @@
       <c r="J18" s="42"/>
       <c r="K18" s="42"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1272,13 +1278,13 @@
       <c r="J19" s="46"/>
       <c r="K19" s="46"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H20" s="18"/>
       <c r="I20" s="18"/>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="G21" s="11" t="s">
         <v>9</v>
       </c>
@@ -1290,7 +1296,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="G22" s="3" t="s">
         <v>10</v>
       </c>
@@ -1299,7 +1305,7 @@
       <c r="J22" s="51"/>
       <c r="K22" s="51"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -1315,7 +1321,7 @@
       <c r="J24" s="43"/>
       <c r="K24" s="43"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" s="11" t="s">
         <v>55</v>
       </c>
@@ -1331,7 +1337,7 @@
       <c r="J25" s="53"/>
       <c r="K25" s="53"/>
     </row>
-    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A26" s="12" t="s">
         <v>4</v>
       </c>
@@ -1350,13 +1356,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H28" s="18"/>
       <c r="I28" s="18"/>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29" s="8" t="s">
         <v>5</v>
       </c>
@@ -1372,7 +1378,7 @@
       <c r="J29" s="56"/>
       <c r="K29" s="56"/>
     </row>
-    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A32" s="62" t="s">
         <v>58</v>
       </c>
@@ -1387,7 +1393,7 @@
       <c r="J32" s="62"/>
       <c r="K32" s="62"/>
     </row>
-    <row r="33" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A33" s="2" t="s">
         <v>11</v>
       </c>
@@ -1419,7 +1425,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" s="3" t="s">
         <v>0</v>
       </c>
@@ -1459,7 +1465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" s="3" t="s">
         <v>36</v>
       </c>
@@ -1502,7 +1508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A36" s="6" t="s">
         <v>4</v>
       </c>
@@ -1542,7 +1548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" s="8" t="s">
         <v>5</v>
       </c>
@@ -1582,7 +1588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A40" s="2" t="s">
         <v>38</v>
       </c>
@@ -1599,7 +1605,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" s="3" t="s">
         <v>19</v>
       </c>
@@ -1608,7 +1614,7 @@
       <c r="D41" s="46"/>
       <c r="E41" s="46"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>42</v>
       </c>
@@ -1620,7 +1626,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>39</v>
       </c>
@@ -1629,7 +1635,7 @@
       <c r="D43" s="57"/>
       <c r="E43" s="57"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>40</v>
       </c>
@@ -1638,7 +1644,7 @@
       <c r="D44" s="58"/>
       <c r="E44" s="58"/>
     </row>
-    <row r="45" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A45" s="26" t="s">
         <v>41</v>
       </c>
@@ -1647,7 +1653,7 @@
       <c r="D45" s="60"/>
       <c r="E45" s="60"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" s="8" t="s">
         <v>38</v>
       </c>
@@ -1656,7 +1662,7 @@
       <c r="D46" s="55"/>
       <c r="E46" s="55"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" s="28" t="s">
         <v>45</v>
       </c>
@@ -1669,7 +1675,7 @@
       <c r="E48" s="63"/>
       <c r="F48" s="63"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" s="28"/>
       <c r="B49" s="36"/>
       <c r="C49" s="61"/>
@@ -1677,13 +1683,13 @@
       <c r="E49" s="61"/>
       <c r="F49" s="61"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="H56" s="18"/>
       <c r="I56" s="18"/>
       <c r="J56" s="18"/>
       <c r="K56" s="18"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="G57" s="8"/>
       <c r="H57" s="21"/>
       <c r="I57" s="21"/>
@@ -1715,13 +1721,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19B808E4-6AC2-46C9-910E-C3B9121AAE5D}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="8.6328125" style="40" customWidth="1"/>
+    <col min="1" max="1" width="24.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="8.59765625" style="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>60</v>
       </c>
@@ -1738,7 +1744,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1759,7 +1765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1780,7 +1786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="26" t="s">
         <v>6</v>
       </c>
@@ -1801,7 +1807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>36</v>
       </c>
@@ -1822,7 +1828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>61</v>
       </c>
@@ -1850,13 +1856,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4C7060-AB49-423F-8EF8-B072503A9C7A}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="8.6328125" customWidth="1"/>
+    <col min="1" max="1" width="21.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="8.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -1873,7 +1879,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -1893,7 +1899,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -1913,7 +1919,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="12" t="s">
         <v>57</v>
       </c>
@@ -1942,13 +1948,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38DC4EB-101F-40DF-969D-2263D791CE3A}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="8.6328125" customWidth="1"/>
+    <col min="1" max="1" width="23.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="8.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
@@ -1965,7 +1971,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>51</v>
       </c>
@@ -1982,7 +1988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="30" t="s">
         <v>47</v>
       </c>
@@ -1999,7 +2005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="31" t="s">
         <v>49</v>
       </c>
@@ -2020,7 +2026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -2041,7 +2047,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="15" t="s">
         <v>48</v>
       </c>
@@ -2061,7 +2067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="12" t="s">
         <v>46</v>
       </c>
@@ -2081,7 +2087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="8" t="s">
         <v>15</v>
       </c>
@@ -2102,7 +2108,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -2119,7 +2125,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>51</v>
       </c>
@@ -2136,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="34" t="s">
         <v>13</v>
       </c>
@@ -2153,7 +2159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="28" t="s">
         <v>9</v>
       </c>

--- a/assets/fcf/Financial Statements & Free Cash Flow.xlsx
+++ b/assets/fcf/Financial Statements & Free Cash Flow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\5 - Financial Statements &amp; Free Cash Flow\1 - Async\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\Financial Analytics Spring 2025\Course\3 - Financial Statements &amp; Free Cash Flow\1 - Async\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CB26C1-CB3D-4E92-92FC-7A3F89469874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED32450-9FBA-476D-93F6-82A8D0111D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" activeTab="1" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Description" sheetId="9" r:id="rId1"/>
@@ -252,9 +252,6 @@
     <t>You are going to start a pizza business.</t>
   </si>
   <si>
-    <t>You will raise capital will come from three sources:</t>
-  </si>
-  <si>
     <t>2. You will sell $60 of long-term bonds. You will repay $20 each year over the thee three years. Both the LoC and bond have a cost of debt of 5%.</t>
   </si>
   <si>
@@ -295,6 +292,9 @@
   </si>
   <si>
     <t>=EBIT</t>
+  </si>
+  <si>
+    <t>You will raise capital from three sources:</t>
   </si>
 </sst>
 </file>
@@ -554,6 +554,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -561,9 +564,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -903,81 +903,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CDAEB0D-3A27-486D-AC6C-E43C29FCDDD3}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -988,18 +988,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4551FB90-26B1-44C9-90FF-AB3D820DD8A7}">
   <dimension ref="A1:L57"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.06640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="7.59765625" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.796875" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="6.06640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="53.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.08984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="7.6328125" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.81640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="53.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="64" t="s">
         <v>16</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="65" t="s">
         <v>17</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="66" t="s">
         <v>30</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="67" t="s">
         <v>18</v>
       </c>
@@ -1077,17 +1077,17 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" s="71" t="s">
-        <v>84</v>
-      </c>
-      <c r="B5" s="68"/>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="68" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="69"/>
       <c r="C5" s="43"/>
       <c r="D5" s="43"/>
       <c r="E5" s="43"/>
       <c r="J5" s="24"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="67" t="s">
         <v>20</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="66" t="s">
         <v>21</v>
       </c>
@@ -1108,7 +1108,7 @@
       <c r="D7" s="43"/>
       <c r="E7" s="43"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="67" t="s">
         <v>22</v>
       </c>
@@ -1120,31 +1120,31 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" s="69" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="69"/>
+      <c r="B9" s="70"/>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
       <c r="E9" s="45"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A10" s="70" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="70"/>
+      <c r="B10" s="71"/>
       <c r="C10" s="43"/>
       <c r="D10" s="43"/>
       <c r="E10" s="43"/>
       <c r="F10" s="27"/>
       <c r="G10" s="27"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A11" s="70" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="70"/>
+      <c r="B11" s="71"/>
       <c r="C11" s="43"/>
       <c r="D11" s="43"/>
       <c r="E11" s="43"/>
@@ -1152,7 +1152,7 @@
       <c r="G11" s="27"/>
       <c r="I11" s="29"/>
     </row>
-    <row r="14" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="62" t="s">
         <v>59</v>
       </c>
@@ -1167,7 +1167,7 @@
       <c r="J14" s="62"/>
       <c r="K14" s="62"/>
     </row>
-    <row r="15" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>0</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>1</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
         <v>2</v>
       </c>
@@ -1262,7 +1262,7 @@
       <c r="J18" s="42"/>
       <c r="K18" s="42"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1278,13 +1278,13 @@
       <c r="J19" s="46"/>
       <c r="K19" s="46"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="H20" s="18"/>
       <c r="I20" s="18"/>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G21" s="11" t="s">
         <v>9</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G22" s="3" t="s">
         <v>10</v>
       </c>
@@ -1305,7 +1305,7 @@
       <c r="J22" s="51"/>
       <c r="K22" s="51"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -1321,7 +1321,7 @@
       <c r="J24" s="43"/>
       <c r="K24" s="43"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
         <v>55</v>
       </c>
@@ -1337,7 +1337,7 @@
       <c r="J25" s="53"/>
       <c r="K25" s="53"/>
     </row>
-    <row r="26" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="12" t="s">
         <v>4</v>
       </c>
@@ -1356,13 +1356,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="H28" s="18"/>
       <c r="I28" s="18"/>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
         <v>5</v>
       </c>
@@ -1378,7 +1378,7 @@
       <c r="J29" s="56"/>
       <c r="K29" s="56"/>
     </row>
-    <row r="32" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="62" t="s">
         <v>58</v>
       </c>
@@ -1393,7 +1393,7 @@
       <c r="J32" s="62"/>
       <c r="K32" s="62"/>
     </row>
-    <row r="33" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
         <v>11</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>0</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>36</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
         <v>4</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>5</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>38</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>19</v>
       </c>
@@ -1614,7 +1614,7 @@
       <c r="D41" s="46"/>
       <c r="E41" s="46"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>42</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>39</v>
       </c>
@@ -1635,7 +1635,7 @@
       <c r="D43" s="57"/>
       <c r="E43" s="57"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>40</v>
       </c>
@@ -1644,7 +1644,7 @@
       <c r="D44" s="58"/>
       <c r="E44" s="58"/>
     </row>
-    <row r="45" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="26" t="s">
         <v>41</v>
       </c>
@@ -1653,7 +1653,7 @@
       <c r="D45" s="60"/>
       <c r="E45" s="60"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
         <v>38</v>
       </c>
@@ -1662,7 +1662,7 @@
       <c r="D46" s="55"/>
       <c r="E46" s="55"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="28" t="s">
         <v>45</v>
       </c>
@@ -1675,7 +1675,7 @@
       <c r="E48" s="63"/>
       <c r="F48" s="63"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="28"/>
       <c r="B49" s="36"/>
       <c r="C49" s="61"/>
@@ -1683,13 +1683,13 @@
       <c r="E49" s="61"/>
       <c r="F49" s="61"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="H56" s="18"/>
       <c r="I56" s="18"/>
       <c r="J56" s="18"/>
       <c r="K56" s="18"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="G57" s="8"/>
       <c r="H57" s="21"/>
       <c r="I57" s="21"/>
@@ -1721,13 +1721,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19B808E4-6AC2-46C9-910E-C3B9121AAE5D}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.53125" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="8.59765625" style="40" customWidth="1"/>
+    <col min="1" max="1" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="8.6328125" style="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>60</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="26" t="s">
         <v>6</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>36</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>61</v>
       </c>
@@ -1856,13 +1856,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4C7060-AB49-423F-8EF8-B072503A9C7A}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="8.59765625" customWidth="1"/>
+    <col min="1" max="1" width="21.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12" t="s">
         <v>57</v>
       </c>
@@ -1948,13 +1948,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38DC4EB-101F-40DF-969D-2263D791CE3A}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="8.59765625" customWidth="1"/>
+    <col min="1" max="1" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>51</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>47</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="31" t="s">
         <v>49</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>48</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
         <v>46</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>15</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>51</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="34" t="s">
         <v>13</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="28" t="s">
         <v>9</v>
       </c>
